--- a/input/acad.xlsx
+++ b/input/acad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jelizalde\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\DIP\bases-datos-dip\input\data\original\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4CEB0F-6626-4CDE-B890-60948384F729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F18749B-22B2-4827-B6EF-D3B364D318D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exportar Hoja de Trabajo" sheetId="1" r:id="rId1"/>
@@ -3310,7 +3310,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -3368,7 +3368,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
